--- a/frontend/aims-uix3/public/일괄등록_샘플.xlsx
+++ b/frontend/aims-uix3/public/일괄등록_샘플.xlsx
@@ -400,13 +400,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E16"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="40.83203125" customWidth="1"/>
-    <col min="4" max="4" width="6.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -690,11 +683,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="45.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -827,18 +815,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J20"/>
-  <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -877,7 +853,7 @@
         <v>홍길동</v>
       </c>
       <c r="B2" t="str">
-        <v>마스터플랜변액유니버셜종신보험</v>
+        <v>무배당 마스터플랜 변액유니버셜종신보험</v>
       </c>
       <c r="C2" t="str">
         <v>2024-01-15</v>
@@ -909,7 +885,7 @@
         <v>김영희</v>
       </c>
       <c r="B3" t="str">
-        <v>미리받는 변액종신보험 공감</v>
+        <v>무배당 미리받는 변액종신보험 공감</v>
       </c>
       <c r="C3" t="str">
         <v>2023-06-20</v>
@@ -941,7 +917,7 @@
         <v>이철수</v>
       </c>
       <c r="B4" t="str">
-        <v>360 종합보장보험</v>
+        <v>무배당 360 종합보장보험(무해약환급금형)</v>
       </c>
       <c r="C4" t="str">
         <v>2022-03-10</v>
@@ -973,7 +949,7 @@
         <v>박민지</v>
       </c>
       <c r="B5" t="str">
-        <v>하이라이프종신보험</v>
+        <v>무배당 하이라이프종신보험</v>
       </c>
       <c r="C5" t="str">
         <v>2024-02-28</v>
@@ -1005,7 +981,7 @@
         <v>최준혁</v>
       </c>
       <c r="B6" t="str">
-        <v>백만인을위한 달러종신보험</v>
+        <v>무배당 백만인을위한달러종신보험(저해약환급금형)</v>
       </c>
       <c r="C6" t="str">
         <v>2023-11-05</v>
@@ -1069,7 +1045,7 @@
         <v>강동원</v>
       </c>
       <c r="B8" t="str">
-        <v>변액유니버셜 오늘의 종신보험</v>
+        <v>무배당 변액유니버셜오늘의종신보험</v>
       </c>
       <c r="C8" t="str">
         <v>2023-08-22</v>
@@ -1101,7 +1077,7 @@
         <v>윤서현</v>
       </c>
       <c r="B9" t="str">
-        <v>아이사랑 첫보험</v>
+        <v>무배당 아이사랑 첫보험</v>
       </c>
       <c r="C9" t="str">
         <v>2024-01-30</v>
@@ -1133,7 +1109,7 @@
         <v>임재현</v>
       </c>
       <c r="B10" t="str">
-        <v>100%만족하는달러종신보험</v>
+        <v>무배당 100% 만족하는 달러종신보험(저해지환급금형)</v>
       </c>
       <c r="C10" t="str">
         <v>2023-09-15</v>
@@ -1165,7 +1141,7 @@
         <v>송지원</v>
       </c>
       <c r="B11" t="str">
-        <v>Life Cycle 선지급종신보험</v>
+        <v>무배당 Life Cycle 선지급종신보험</v>
       </c>
       <c r="C11" t="str">
         <v>2024-04-01</v>
@@ -1197,7 +1173,7 @@
         <v>(주)테크솔루션</v>
       </c>
       <c r="B12" t="str">
-        <v>메트라이프정기보험</v>
+        <v>무배당 메트라이프정기보험</v>
       </c>
       <c r="C12" t="str">
         <v>2023-07-10</v>
@@ -1229,7 +1205,7 @@
         <v>한승우</v>
       </c>
       <c r="B13" t="str">
-        <v>무배당 변액유니버셜 오늘의 종신보험 Plus</v>
+        <v>무배당 변액유니버셜오늘의종신보험 Plus</v>
       </c>
       <c r="C13" t="str">
         <v>2024-02-14</v>
@@ -1261,7 +1237,7 @@
         <v>오하나</v>
       </c>
       <c r="B14" t="str">
-        <v>360암보험(갱신형)</v>
+        <v>무배당 360 암보험(갱신형)</v>
       </c>
       <c r="C14" t="str">
         <v>2023-10-25</v>
@@ -1293,7 +1269,7 @@
         <v>신동혁</v>
       </c>
       <c r="B15" t="str">
-        <v>유니버셜달러종신보험</v>
+        <v>무배당 유니버셜달러종신보험(보증형)</v>
       </c>
       <c r="C15" t="str">
         <v>2024-03-08</v>
@@ -1325,7 +1301,7 @@
         <v>배수지</v>
       </c>
       <c r="B16" t="str">
-        <v>실버플랜변액유니버셜보험</v>
+        <v>무배당 실버플랜 변액유니버셜보험(1종-월납)</v>
       </c>
       <c r="C16" t="str">
         <v>2023-05-18</v>
@@ -1357,7 +1333,7 @@
         <v>조민수</v>
       </c>
       <c r="B17" t="str">
-        <v>암엔암보험</v>
+        <v>무배당 암엔암보험(기본형)</v>
       </c>
       <c r="C17" t="str">
         <v>2024-01-22</v>
@@ -1389,7 +1365,7 @@
         <v>홍길동</v>
       </c>
       <c r="B18" t="str">
-        <v>100세시대간편건강보험</v>
+        <v>무배당 100세시대간편건강보험(유해지환급형)</v>
       </c>
       <c r="C18" t="str">
         <v>2020-06-10</v>
@@ -1421,7 +1397,7 @@
         <v>김영희</v>
       </c>
       <c r="B19" t="str">
-        <v>My fund변액종신보험</v>
+        <v>무배당 My Fund 변액종신보험</v>
       </c>
       <c r="C19" t="str">
         <v>2021-08-15</v>
@@ -1453,7 +1429,7 @@
         <v>이철수</v>
       </c>
       <c r="B20" t="str">
-        <v>꿈돌이사랑2보험</v>
+        <v>무배당 꿈돌이사랑Ⅱ보험</v>
       </c>
       <c r="C20" t="str">
         <v>2019-04-20</v>

--- a/frontend/aims-uix3/public/일괄등록_샘플.xlsx
+++ b/frontend/aims-uix3/public/일괄등록_샘플.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aims\frontend\aims-uix3\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\rossi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894B74E9-8D10-416B-B0D1-6FBD2D51F336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E72680-5094-4C16-9D27-F33FC1C5AB6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1770" yWindow="1395" windowWidth="23415" windowHeight="13950" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4860" yWindow="885" windowWidth="23415" windowHeight="13950" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="개인고객" sheetId="1" r:id="rId1"/>
@@ -272,40 +272,40 @@
     <t>대표자명</t>
   </si>
   <si>
-    <t>(주)테크솔루션</t>
-  </si>
-  <si>
-    <t>contact@techsolution.co.kr</t>
+    <t>(주)행복산업</t>
+  </si>
+  <si>
+    <t>info@happyind.co.kr</t>
   </si>
   <si>
     <t>02-1234-5678</t>
   </si>
   <si>
-    <t>서울시 강남구 테헤란로 123 테크빌딩 5층</t>
+    <t>서울시 강남구 테헤란로 123</t>
   </si>
   <si>
     <t>123-45-67890</t>
   </si>
   <si>
-    <t>김태호</t>
-  </si>
-  <si>
-    <t>삼성전자(주)</t>
-  </si>
-  <si>
-    <t>info@samsung.com</t>
+    <t>김대표</t>
+  </si>
+  <si>
+    <t>미래전자(주)</t>
+  </si>
+  <si>
+    <t>contact@miraeelec.co.kr</t>
   </si>
   <si>
     <t>02-2345-6789</t>
   </si>
   <si>
-    <t>경기도 수원시 영통구 삼성로 456</t>
+    <t>경기도 수원시 영통구 산업로 456</t>
   </si>
   <si>
     <t>234-56-78901</t>
   </si>
   <si>
-    <t>(주)현대모비스</t>
+    <t>(주)푸른기술</t>
   </si>
   <si>
     <t>02-3456-7890</t>
@@ -317,13 +317,13 @@
     <t>345-67-89012</t>
   </si>
   <si>
-    <t>정의선</t>
-  </si>
-  <si>
-    <t>LG화학(주)</t>
-  </si>
-  <si>
-    <t>lg@lgchem.com</t>
+    <t>이사장</t>
+  </si>
+  <si>
+    <t>청솔화학(주)</t>
+  </si>
+  <si>
+    <t>cs@chungsol.co.kr</t>
   </si>
   <si>
     <t>02-4567-8901</t>
@@ -332,13 +332,13 @@
     <t>서울시 영등포구 여의대로 234</t>
   </si>
   <si>
-    <t>신학철</t>
-  </si>
-  <si>
-    <t>SK텔레콤(주)</t>
-  </si>
-  <si>
-    <t>sk@sktelecom.com</t>
+    <t>박회장</t>
+  </si>
+  <si>
+    <t>동방통신(주)</t>
+  </si>
+  <si>
+    <t>db@dongbang.co.kr</t>
   </si>
   <si>
     <t>02-5678-9012</t>
@@ -350,10 +350,10 @@
     <t>567-89-01234</t>
   </si>
   <si>
-    <t>박정호</t>
-  </si>
-  <si>
-    <t>(주)카카오</t>
+    <t>최대표</t>
+  </si>
+  <si>
+    <t>(주)별빛소프트</t>
   </si>
   <si>
     <t>02-6789-0123</t>
@@ -365,10 +365,10 @@
     <t>678-90-12345</t>
   </si>
   <si>
-    <t>네이버(주)</t>
-  </si>
-  <si>
-    <t>naver@naver.com</t>
+    <t>하늘미디어(주)</t>
+  </si>
+  <si>
+    <t>sky@hanulmedia.co.kr</t>
   </si>
   <si>
     <t>02-7890-1234</t>
@@ -380,13 +380,13 @@
     <t>789-01-23456</t>
   </si>
   <si>
-    <t>최수연</t>
-  </si>
-  <si>
-    <t>(주)쿠팡</t>
-  </si>
-  <si>
-    <t>coupang@coupang.com</t>
+    <t>정사장</t>
+  </si>
+  <si>
+    <t>(주)바다유통</t>
+  </si>
+  <si>
+    <t>sea@badayutong.co.kr</t>
   </si>
   <si>
     <t>02-8901-2345</t>
@@ -395,10 +395,10 @@
     <t>서울시 송파구 송파대로 456</t>
   </si>
   <si>
-    <t>김범석</t>
-  </si>
-  <si>
-    <t>(주)배달의민족</t>
+    <t>강대표</t>
+  </si>
+  <si>
+    <t>(주)산들식품</t>
   </si>
   <si>
     <t>02-9012-3456</t>
@@ -410,13 +410,13 @@
     <t>901-23-45678</t>
   </si>
   <si>
-    <t>김봉진</t>
-  </si>
-  <si>
-    <t>(주)토스</t>
-  </si>
-  <si>
-    <t>toss@toss.im</t>
+    <t>윤회장</t>
+  </si>
+  <si>
+    <t>(주)새벽금융</t>
+  </si>
+  <si>
+    <t>dawn@saebyuk.co.kr</t>
   </si>
   <si>
     <t>02-0123-4567</t>
@@ -1136,7 +1136,6 @@
     <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1475,9 +1474,9 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1714,17 +1713,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
